--- a/00 - DOCUMENTS/FPGA/pinout.xlsx
+++ b/00 - DOCUMENTS/FPGA/pinout.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repositorio_remoto\FPGAging_Lite\00 - DOCUMENTS\FPGA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorio_Remoto\FPGAging_Lite\00 - DOCUMENTS\FPGA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAAA2A48-5D91-4DB7-9B5E-50824729CB43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1183A102-2C2D-4A00-BDFE-7365EE0C2F20}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="17385" yWindow="1110" windowWidth="12150" windowHeight="11385" xr2:uid="{99057691-B5E5-4BCE-BD5B-98BE37669580}"/>
   </bookViews>
@@ -3144,41 +3144,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1E60DBDC-DEFB-42DE-9947-DC0D6A763442}" name="xcsu35psbvb625pkg" displayName="xcsu35psbvb625pkg" ref="A1:F628" tableType="queryTable" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1E60DBDC-DEFB-42DE-9947-DC0D6A763442}" name="xcsu35psbvb625pkg" displayName="xcsu35psbvb625pkg" ref="A1:F628" tableType="queryTable" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="A1:F628" xr:uid="{1E60DBDC-DEFB-42DE-9947-DC0D6A763442}">
-    <filterColumn colId="1">
-      <filters blank="1">
-        <filter val="DXN"/>
-        <filter val="DXP"/>
-        <filter val="GNDADC"/>
-        <filter val="NC"/>
-        <filter val="POR_OVERRIDE"/>
-        <filter val="VCCADC"/>
-        <filter val="VCCAUX"/>
-        <filter val="VCCAUX_HDIO"/>
-        <filter val="VCCAUX_HPIO"/>
-        <filter val="VCCBRAM"/>
-        <filter val="VCCINT"/>
-        <filter val="VCCINT_IO"/>
-        <filter val="VN"/>
-        <filter val="VP"/>
-        <filter val="VREFN"/>
-        <filter val="VREFP"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="3">
-      <filters blank="1">
-        <filter val="NA"/>
+      <filters>
+        <filter val="0"/>
       </filters>
     </filterColumn>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{821587FF-51B2-4105-A2AE-82D560319BAD}" uniqueName="1" name="Pin" queryTableFieldId="1" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{D5EFB6E5-AB75-4591-943C-F4463E57773D}" uniqueName="2" name="Pin Name" queryTableFieldId="2" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{1F0DC49F-4CBF-4AB7-9329-6C65414CA082}" uniqueName="3" name="Memory Byte Group" queryTableFieldId="3" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{BA67F6CF-8455-41ED-A937-9BA4F510FFC0}" uniqueName="4" name="Bank" queryTableFieldId="4" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{5C21581F-1114-4C85-ACB0-6DF13A80A429}" uniqueName="5" name="I/O Type" queryTableFieldId="5" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{321A4580-F5D2-4167-87B2-3287026E4E0B}" uniqueName="6" name="Super Logic Region" queryTableFieldId="6" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{821587FF-51B2-4105-A2AE-82D560319BAD}" uniqueName="1" name="Pin" queryTableFieldId="1" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{D5EFB6E5-AB75-4591-943C-F4463E57773D}" uniqueName="2" name="Pin Name" queryTableFieldId="2" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{1F0DC49F-4CBF-4AB7-9329-6C65414CA082}" uniqueName="3" name="Memory Byte Group" queryTableFieldId="3" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{BA67F6CF-8455-41ED-A937-9BA4F510FFC0}" uniqueName="4" name="Bank" queryTableFieldId="4" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{5C21581F-1114-4C85-ACB0-6DF13A80A429}" uniqueName="5" name="I/O Type" queryTableFieldId="5" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{321A4580-F5D2-4167-87B2-3287026E4E0B}" uniqueName="6" name="Super Logic Region" queryTableFieldId="6" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3511,127 +3491,127 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="F3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="F4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="F5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="F6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -3651,7 +3631,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
@@ -3671,27 +3651,27 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="F10" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>27</v>
       </c>
@@ -3711,7 +3691,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>29</v>
       </c>
@@ -3731,7 +3711,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
@@ -3751,7 +3731,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>33</v>
       </c>
@@ -3771,7 +3751,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -3791,7 +3771,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>37</v>
       </c>
@@ -3811,7 +3791,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>39</v>
       </c>
@@ -3831,7 +3811,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>41</v>
       </c>
@@ -3851,7 +3831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>43</v>
       </c>
@@ -3871,7 +3851,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>45</v>
       </c>
@@ -3891,7 +3871,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
@@ -3911,7 +3891,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>49</v>
       </c>
@@ -3931,7 +3911,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>51</v>
       </c>
@@ -3951,7 +3931,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>53</v>
       </c>
@@ -3971,7 +3951,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>55</v>
       </c>
@@ -10091,7 +10071,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="331" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>684</v>
       </c>
@@ -10111,7 +10091,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="332" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>686</v>
       </c>
@@ -10131,7 +10111,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="333" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>687</v>
       </c>
@@ -12851,7 +12831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="469" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>832</v>
       </c>
@@ -12871,7 +12851,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="470" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>834</v>
       </c>
@@ -12891,7 +12871,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="471" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
         <v>836</v>
       </c>
@@ -12911,7 +12891,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="472" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
         <v>838</v>
       </c>
@@ -12931,7 +12911,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="473" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>839</v>
       </c>
@@ -12951,7 +12931,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="474" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
         <v>840</v>
       </c>
@@ -12971,7 +12951,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="475" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>841</v>
       </c>
@@ -12991,7 +12971,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="476" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
         <v>842</v>
       </c>
@@ -13011,7 +12991,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="477" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
         <v>843</v>
       </c>
@@ -13031,7 +13011,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="478" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>844</v>
       </c>
@@ -13051,7 +13031,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="479" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>845</v>
       </c>
@@ -13071,7 +13051,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="480" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
         <v>847</v>
       </c>
@@ -13091,7 +13071,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="481" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>848</v>
       </c>
@@ -13111,7 +13091,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="482" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
         <v>849</v>
       </c>
@@ -13131,7 +13111,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="483" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>850</v>
       </c>
@@ -13151,7 +13131,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="484" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
         <v>851</v>
       </c>
@@ -13171,7 +13151,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="485" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
         <v>852</v>
       </c>
@@ -13191,7 +13171,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="486" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
         <v>853</v>
       </c>
@@ -13211,7 +13191,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="487" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>854</v>
       </c>
@@ -13231,7 +13211,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="488" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>855</v>
       </c>
@@ -13251,7 +13231,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="489" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>856</v>
       </c>
@@ -13271,7 +13251,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="490" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
         <v>857</v>
       </c>
@@ -13291,7 +13271,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="491" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>858</v>
       </c>
@@ -13311,7 +13291,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="492" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>859</v>
       </c>
@@ -13331,7 +13311,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="493" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>860</v>
       </c>
@@ -13351,7 +13331,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="494" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>861</v>
       </c>
@@ -13371,7 +13351,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="495" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
         <v>862</v>
       </c>
@@ -13391,7 +13371,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="496" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>864</v>
       </c>
@@ -13411,7 +13391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="497" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
         <v>865</v>
       </c>
@@ -13431,7 +13411,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="498" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>866</v>
       </c>
@@ -13451,7 +13431,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="499" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>867</v>
       </c>
@@ -13471,7 +13451,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="500" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
         <v>869</v>
       </c>
@@ -13491,7 +13471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="501" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
         <v>870</v>
       </c>
@@ -13511,7 +13491,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="502" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
         <v>871</v>
       </c>
@@ -13531,7 +13511,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="503" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
         <v>872</v>
       </c>
@@ -13551,7 +13531,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="504" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
         <v>873</v>
       </c>
@@ -13571,7 +13551,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="505" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
         <v>875</v>
       </c>
@@ -13591,7 +13571,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="506" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
         <v>876</v>
       </c>
@@ -13611,7 +13591,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="507" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
         <v>877</v>
       </c>
@@ -13631,7 +13611,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="508" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
         <v>878</v>
       </c>
@@ -13651,7 +13631,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="509" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
         <v>879</v>
       </c>
@@ -13671,7 +13651,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="510" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
         <v>880</v>
       </c>
@@ -13691,7 +13671,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="511" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
         <v>881</v>
       </c>
@@ -13711,7 +13691,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="512" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
         <v>882</v>
       </c>
@@ -13731,7 +13711,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="513" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
         <v>883</v>
       </c>
@@ -13751,7 +13731,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="514" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
         <v>884</v>
       </c>
@@ -13771,7 +13751,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="515" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
         <v>885</v>
       </c>
@@ -13791,7 +13771,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="516" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
         <v>886</v>
       </c>
@@ -13811,327 +13791,327 @@
         <v>8</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A517" s="1" t="s">
+    <row r="517" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A517" s="2" t="s">
         <v>887</v>
       </c>
-      <c r="B517" s="1" t="s">
+      <c r="B517" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="C517" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D517" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E517" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F517" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A518" s="1" t="s">
+      <c r="C517" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D517" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E517" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F517" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="518" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A518" s="2" t="s">
         <v>888</v>
       </c>
-      <c r="B518" s="1" t="s">
+      <c r="B518" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="C518" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D518" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E518" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F518" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A519" s="1" t="s">
+      <c r="C518" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D518" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E518" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F518" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="519" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A519" s="2" t="s">
         <v>889</v>
       </c>
-      <c r="B519" s="1" t="s">
+      <c r="B519" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="C519" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D519" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E519" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F519" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A520" s="1" t="s">
+      <c r="C519" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D519" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E519" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F519" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="520" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A520" s="2" t="s">
         <v>890</v>
       </c>
-      <c r="B520" s="1" t="s">
+      <c r="B520" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="C520" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D520" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E520" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F520" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A521" s="1" t="s">
+      <c r="C520" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D520" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E520" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F520" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="521" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A521" s="2" t="s">
         <v>891</v>
       </c>
-      <c r="B521" s="1" t="s">
+      <c r="B521" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="C521" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D521" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E521" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F521" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A522" s="1" t="s">
+      <c r="C521" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D521" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E521" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F521" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="522" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A522" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="B522" s="1" t="s">
+      <c r="B522" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="C522" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D522" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E522" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F522" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A523" s="1" t="s">
+      <c r="C522" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D522" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E522" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F522" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="523" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A523" s="2" t="s">
         <v>893</v>
       </c>
-      <c r="B523" s="1" t="s">
+      <c r="B523" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="C523" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D523" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E523" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F523" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A524" s="1" t="s">
+      <c r="C523" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D523" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E523" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F523" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="524" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A524" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="B524" s="1" t="s">
+      <c r="B524" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="C524" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D524" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E524" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F524" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A525" s="1" t="s">
+      <c r="C524" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D524" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E524" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F524" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="525" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A525" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="B525" s="1" t="s">
+      <c r="B525" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="C525" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D525" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E525" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F525" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A526" s="1" t="s">
+      <c r="C525" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D525" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E525" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F525" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="526" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A526" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="B526" s="1" t="s">
+      <c r="B526" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="C526" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D526" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E526" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F526" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A527" s="1" t="s">
+      <c r="C526" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D526" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E526" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F526" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="527" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A527" s="2" t="s">
         <v>897</v>
       </c>
-      <c r="B527" s="1" t="s">
+      <c r="B527" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="C527" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D527" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E527" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F527" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A528" s="1" t="s">
+      <c r="C527" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D527" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E527" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F527" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="528" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A528" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="B528" s="1" t="s">
+      <c r="B528" s="2" t="s">
         <v>874</v>
       </c>
-      <c r="C528" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D528" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E528" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F528" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A529" s="1" t="s">
+      <c r="C528" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D528" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E528" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F528" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="529" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A529" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="B529" s="1" t="s">
+      <c r="B529" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="C529" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D529" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E529" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F529" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A530" s="1" t="s">
+      <c r="C529" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D529" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E529" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F529" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="530" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A530" s="2" t="s">
         <v>901</v>
       </c>
-      <c r="B530" s="1" t="s">
+      <c r="B530" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="C530" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D530" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E530" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F530" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A531" s="1" t="s">
+      <c r="C530" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D530" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E530" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F530" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="531" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A531" s="2" t="s">
         <v>902</v>
       </c>
-      <c r="B531" s="1" t="s">
+      <c r="B531" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="C531" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D531" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E531" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F531" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A532" s="1" t="s">
+      <c r="C531" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D531" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E531" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F531" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="532" spans="1:6" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A532" s="2" t="s">
         <v>903</v>
       </c>
-      <c r="B532" s="1" t="s">
+      <c r="B532" s="2" t="s">
         <v>900</v>
       </c>
-      <c r="C532" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D532" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E532" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F532" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C532" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D532" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E532" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F532" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="533" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>904</v>
       </c>
@@ -14151,7 +14131,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>906</v>
       </c>
@@ -14171,7 +14151,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>907</v>
       </c>
@@ -14191,7 +14171,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>908</v>
       </c>
@@ -14211,7 +14191,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>909</v>
       </c>
@@ -14231,7 +14211,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>910</v>
       </c>
@@ -14251,7 +14231,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>911</v>
       </c>
@@ -14271,7 +14251,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>912</v>
       </c>
@@ -14291,7 +14271,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>913</v>
       </c>
@@ -14311,7 +14291,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>914</v>
       </c>
@@ -14331,7 +14311,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>915</v>
       </c>
@@ -14351,7 +14331,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>916</v>
       </c>
@@ -14371,7 +14351,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>917</v>
       </c>
@@ -14391,7 +14371,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>918</v>
       </c>
@@ -14411,7 +14391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>919</v>
       </c>
@@ -14431,7 +14411,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>920</v>
       </c>
@@ -14451,7 +14431,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>921</v>
       </c>
@@ -14471,7 +14451,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>922</v>
       </c>
@@ -14491,7 +14471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>923</v>
       </c>
@@ -14511,7 +14491,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>924</v>
       </c>
@@ -14531,7 +14511,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>925</v>
       </c>
@@ -14551,7 +14531,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>926</v>
       </c>
@@ -14571,7 +14551,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>927</v>
       </c>
@@ -14591,7 +14571,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>928</v>
       </c>
@@ -14611,7 +14591,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>929</v>
       </c>
@@ -14631,7 +14611,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>930</v>
       </c>
@@ -14651,7 +14631,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>931</v>
       </c>
@@ -14671,7 +14651,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>932</v>
       </c>
@@ -14691,7 +14671,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>933</v>
       </c>
@@ -14711,7 +14691,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>934</v>
       </c>
@@ -14731,7 +14711,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>935</v>
       </c>
@@ -14751,7 +14731,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>936</v>
       </c>
@@ -14771,7 +14751,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>937</v>
       </c>
@@ -14791,7 +14771,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>938</v>
       </c>
@@ -14811,7 +14791,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>939</v>
       </c>
@@ -14831,7 +14811,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>940</v>
       </c>
@@ -14851,7 +14831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>941</v>
       </c>
@@ -14871,7 +14851,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>942</v>
       </c>
@@ -14891,7 +14871,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>943</v>
       </c>
@@ -14911,7 +14891,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>944</v>
       </c>
@@ -14931,7 +14911,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>945</v>
       </c>
@@ -14951,7 +14931,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>946</v>
       </c>
@@ -14971,7 +14951,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>947</v>
       </c>
@@ -14991,7 +14971,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>948</v>
       </c>
@@ -15011,7 +14991,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>949</v>
       </c>
@@ -15031,7 +15011,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>950</v>
       </c>
@@ -15051,7 +15031,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>951</v>
       </c>
@@ -15071,7 +15051,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>952</v>
       </c>
@@ -15091,7 +15071,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>953</v>
       </c>
@@ -15111,7 +15091,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>954</v>
       </c>
@@ -15131,7 +15111,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>955</v>
       </c>
@@ -15151,7 +15131,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>956</v>
       </c>
@@ -15171,7 +15151,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>957</v>
       </c>
@@ -15191,7 +15171,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>958</v>
       </c>
@@ -15211,7 +15191,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>959</v>
       </c>
@@ -15231,7 +15211,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>960</v>
       </c>
@@ -15251,7 +15231,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>961</v>
       </c>
@@ -15271,7 +15251,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>962</v>
       </c>
@@ -15291,7 +15271,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>963</v>
       </c>
@@ -15311,7 +15291,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>964</v>
       </c>
@@ -15331,7 +15311,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>965</v>
       </c>
@@ -15351,7 +15331,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>966</v>
       </c>
@@ -15371,7 +15351,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>967</v>
       </c>
@@ -15391,7 +15371,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>968</v>
       </c>
@@ -15411,7 +15391,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>969</v>
       </c>
@@ -15431,7 +15411,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>970</v>
       </c>
@@ -15451,7 +15431,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>971</v>
       </c>
@@ -15471,7 +15451,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>972</v>
       </c>
@@ -15491,7 +15471,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>973</v>
       </c>
@@ -15511,7 +15491,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>974</v>
       </c>
@@ -15531,7 +15511,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>975</v>
       </c>
@@ -15551,7 +15531,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>976</v>
       </c>
@@ -15571,7 +15551,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>977</v>
       </c>
@@ -15591,7 +15571,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>978</v>
       </c>
@@ -15611,7 +15591,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="607" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>979</v>
       </c>
@@ -15631,7 +15611,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>980</v>
       </c>
@@ -15651,7 +15631,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>981</v>
       </c>
@@ -15671,7 +15651,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="610" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>982</v>
       </c>
@@ -15691,7 +15671,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>983</v>
       </c>
@@ -15711,7 +15691,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>984</v>
       </c>
@@ -15731,7 +15711,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="613" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>985</v>
       </c>
@@ -15751,7 +15731,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>986</v>
       </c>
@@ -15771,7 +15751,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>987</v>
       </c>
@@ -15791,7 +15771,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>988</v>
       </c>
@@ -15811,7 +15791,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>989</v>
       </c>
@@ -15831,7 +15811,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>990</v>
       </c>
@@ -15851,7 +15831,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="619" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>991</v>
       </c>
@@ -15871,7 +15851,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>992</v>
       </c>
@@ -15891,7 +15871,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>993</v>
       </c>
@@ -15911,7 +15891,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="622" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>994</v>
       </c>
@@ -15931,7 +15911,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>995</v>
       </c>
@@ -15951,7 +15931,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>996</v>
       </c>
@@ -15971,7 +15951,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="625" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
         <v>997</v>
       </c>
@@ -15991,7 +15971,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="626" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
         <v>998</v>
       </c>
@@ -16011,7 +15991,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="627" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" s="1"/>
       <c r="B627" s="1"/>
       <c r="C627" s="1"/>
@@ -16019,7 +15999,7 @@
       <c r="E627" s="1"/>
       <c r="F627" s="1"/>
     </row>
-    <row r="628" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" s="1"/>
       <c r="B628" s="1"/>
       <c r="C628" s="1"/>
